--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-01-2026.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>£11.65</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£19.22</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>£32.15</t>
+          <t>£35.33</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>£38.0</t>
+          <t>£40.47</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>£38.5</t>
+          <t>£41.27</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>£940.8</t>
+          <t>£945.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>£26.89</t>
+          <t>£28.31</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.14</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>£33.87</t>
+          <t>£35.65</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>£35.57</t>
+          <t>£37.44</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>£42.58</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>£43.08</t>
+          <t>£43.39</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
